--- a/tests/fixtures/hand_calc/hand_calc_workbook.xlsx
+++ b/tests/fixtures/hand_calc/hand_calc_workbook.xlsx
@@ -612,7 +612,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>profit_if_overdue_unpaid = profit last 12m with each overdue-unpaid invoice removed completely (take away its revenue AND its late cost).</t>
+          <t>profit_if_overdue_unpaid = profit last 12m as if each overdue-unpaid invoice had never been issued: its revenue is gone and so is its late cost, which raises profit. In numbers: profit last 12m - invoice amount + that invoice's late cost (D-16).</t>
         </is>
       </c>
     </row>
@@ -689,6 +689,7 @@
         <v>537.6</v>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
